--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96050</v>
+        <v>96051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96052</v>
+        <v>96056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96056</v>
+        <v>96058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96058</v>
+        <v>96062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96062</v>
+        <v>96070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96070</v>
+        <v>96073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96073</v>
+        <v>96102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129341690</v>
       </c>
       <c r="B3" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129348966</v>
       </c>
       <c r="B4" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129348907</v>
+        <v>129341690</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster om Nedre Herrgölen, Ög</t>
+          <t>Marsammasjön, Marsammasjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567375</v>
+        <v>567406</v>
       </c>
       <c r="R2" t="n">
-        <v>6507486</v>
+        <v>6507501</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341690</v>
+        <v>129341822</v>
       </c>
       <c r="B3" t="n">
-        <v>96263</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567406</v>
+        <v>567385</v>
       </c>
       <c r="R3" t="n">
-        <v>6507501</v>
+        <v>6507464</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,51 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129348966</v>
+        <v>129341585</v>
       </c>
       <c r="B4" t="n">
-        <v>91614</v>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster om Nedre Herrgölen, Ög</t>
+          <t>Marsammasjön, Marsammasjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567375</v>
+        <v>567407</v>
       </c>
       <c r="R4" t="n">
-        <v>6507486</v>
+        <v>6507511</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +948,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -983,7 +969,7 @@
         <v>129341760</v>
       </c>
       <c r="B5" t="n">
-        <v>96120</v>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,6 +1060,330 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129348966</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väster om Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6507486</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129348907</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väster om Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567375</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6507486</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129342144</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nedre herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567378</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6507449</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44620-2025 artfynd.xlsx
+++ b/artfynd/A 44620-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341585</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341760</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129348966</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129348907</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,8 +1419,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342144</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>